--- a/premise/data/additional_inventories/lci-batteries-ASSB.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-ASSB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H364"/>
+  <dimension ref="A1:I436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="75" customWidth="1" min="1" max="1"/>
@@ -6434,7 +6434,9 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>One nominal installed kWh = 8.065117901632592 kg pack * 0.72591 kg cells/kg pack * 0.1708073285047623 kWh/kg cell. Published baseline cell design held constant at all scenario years. Manufacturing and end-of-life pack masses match. Cycle life/replacements belong to the consuming vehicle; no chemistry-specific lifetime is inferred.</t>
+          <t>APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+One nominal installed kWh = 8.065117901632592 kg pack * 0.72591 kg cells/kg pack * 0.1708073285047623 kWh/kg cell. Published baseline cell design held constant at all scenario years. Manufacturing and end-of-life pack masses match. Cycle life/replacements belong to the consuming vehicle; no chemistry-specific lifetime is inferred.</t>
         </is>
       </c>
     </row>
@@ -6540,11 +6542,11 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>market for battery, ASSB, polymer</t>
+          <t>battery hardware, ASSB polymer, separated-controls engineering reference</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>8.065117901632592</v>
+        <v>7.696378455192915</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -6563,7 +6565,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>battery, ASSB, polymer</t>
+          <t>battery hardware, ASSB polymer, separated-controls engineering reference</t>
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
@@ -6575,7 +6577,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>-8.065117901632592</v>
+        <v>-7.696378455192915</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -6600,6 +6602,36 @@
       <c r="H248" t="inlineStr">
         <is>
           <t>Equal-mass generic Li-ion end-of-life treatment proxy; no ASSB-specific recovery yield claimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
+      <c r="B249">
+        <v>0.0563994258855426</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7647,9 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>One nominal installed kWh = 4.357203948791617 kg pack * 0.72591 kg cells/kg pack * 0.3161617539697314 kWh/kg cell. Published baseline cell design held constant at all scenario years. Manufacturing and end-of-life pack masses match. Cycle life/replacements belong to the consuming vehicle; no chemistry-specific lifetime is inferred.</t>
+          <t>APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+One nominal installed kWh = 4.357203948791617 kg pack * 0.72591 kg cells/kg pack * 0.3161617539697314 kWh/kg cell. Published baseline cell design held constant at all scenario years. Manufacturing and end-of-life pack masses match. Cycle life/replacements belong to the consuming vehicle; no chemistry-specific lifetime is inferred.</t>
         </is>
       </c>
     </row>
@@ -7721,11 +7755,11 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>market for battery, ASSB, oxidic</t>
+          <t>battery hardware, ASSB oxidic, separated-controls engineering reference</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>4.357203948791617</v>
+        <v>4.157991365454557</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -7744,7 +7778,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>battery, ASSB, oxidic</t>
+          <t>battery hardware, ASSB oxidic, separated-controls engineering reference</t>
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
@@ -7756,7 +7790,7 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>-4.357203948791617</v>
+        <v>-4.157991365454557</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -7781,6 +7815,36 @@
       <c r="H306" t="inlineStr">
         <is>
           <t>Equal-mass generic Li-ion end-of-life treatment proxy; no ASSB-specific recovery yield claimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
+      <c r="B307">
+        <v>0.030469957683857463</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8860,9 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>One nominal installed kWh = 4.350854113378415 kg pack * 0.72591 kg cells/kg pack * 0.3166231748883239 kWh/kg cell. Published baseline cell design held constant at all scenario years. Manufacturing and end-of-life pack masses match. Cycle life/replacements belong to the consuming vehicle; no chemistry-specific lifetime is inferred.</t>
+          <t>APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+One nominal installed kWh = 4.350854113378415 kg pack * 0.72591 kg cells/kg pack * 0.3166231748883239 kWh/kg cell. Published baseline cell design held constant at all scenario years. Manufacturing and end-of-life pack masses match. Cycle life/replacements belong to the consuming vehicle; no chemistry-specific lifetime is inferred.</t>
         </is>
       </c>
     </row>
@@ -8902,11 +8968,11 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>market for battery, ASSB, sulfidic</t>
+          <t>battery hardware, ASSB sulfidic, separated-controls engineering reference</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>4.350854113378415</v>
+        <v>4.151931846292625</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -8925,7 +8991,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>battery, ASSB, sulfidic</t>
+          <t>battery hardware, ASSB sulfidic, separated-controls engineering reference</t>
         </is>
       </c>
       <c r="H363" t="inlineStr"/>
@@ -8937,7 +9003,7 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>-4.350854113378415</v>
+        <v>-4.151931846292625</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -8962,6 +9028,1809 @@
       <c r="H364" t="inlineStr">
         <is>
           <t>Equal-mass generic Li-ion end-of-life treatment proxy; no ASSB-specific recovery yield claimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
+      <c r="B365">
+        <v>0.030425553240408496</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB polymer, separated-controls engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB polymer, separated-controls engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB polymer, separated-controls engineering reference</t>
+        </is>
+      </c>
+      <c r="B376">
+        <v>1</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB polymer, separated-controls engineering reference</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB polymer, separated-controls engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>battery cell production, ASSB, polymer</t>
+        </is>
+      </c>
+      <c r="B377">
+        <v>0.7606889097331125</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>battery cell, ASSB, polymer</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>battery cell, ASSB, polymer</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B378">
+        <v>0.003299967301479221</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B379">
+        <v>0.003299967301479221</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B380">
+        <v>0.17940399156311074</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B381">
+        <v>0.17940399156311074</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B382">
+        <v>0.00539417731972565</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B383">
+        <v>0.0006980700060821429</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B384">
+        <v>0.00596532550652013</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B385">
+        <v>0.00596532550652013</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+        </is>
+      </c>
+      <c r="B386">
+        <v>0.02227477928498474</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B387">
+        <v>0.02227477928498474</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B388">
+        <v>1</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB oxidic, separated-controls engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B393">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB oxidic, separated-controls engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB oxidic, separated-controls engineering reference</t>
+        </is>
+      </c>
+      <c r="B400">
+        <v>1</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB oxidic, separated-controls engineering reference</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB oxidic, separated-controls engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>battery cell production, ASSB, oxidic</t>
+        </is>
+      </c>
+      <c r="B401">
+        <v>0.7606889097331125</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>battery cell, ASSB, oxidic</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>battery cell, ASSB, oxidic</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B402">
+        <v>0.003299967301479221</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B403">
+        <v>0.003299967301479221</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B404">
+        <v>0.17940399156311074</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B405">
+        <v>0.17940399156311074</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B406">
+        <v>0.00539417731972565</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B407">
+        <v>0.0006980700060821429</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B408">
+        <v>0.00596532550652013</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B409">
+        <v>0.00596532550652013</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+        </is>
+      </c>
+      <c r="B410">
+        <v>0.02227477928498474</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B411">
+        <v>0.02227477928498474</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B412">
+        <v>1</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB sulfidic, separated-controls engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B417">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB sulfidic, separated-controls engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB sulfidic, separated-controls engineering reference</t>
+        </is>
+      </c>
+      <c r="B424">
+        <v>1</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB sulfidic, separated-controls engineering reference</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>battery hardware, ASSB sulfidic, separated-controls engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>battery cell production, ASSB, sulfidic</t>
+        </is>
+      </c>
+      <c r="B425">
+        <v>0.7606889097331125</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>battery cell, ASSB, sulfidic</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>battery cell, ASSB, sulfidic</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B426">
+        <v>0.003299967301479221</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B427">
+        <v>0.003299967301479221</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B428">
+        <v>0.17940399156311074</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B429">
+        <v>0.17940399156311074</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B430">
+        <v>0.00539417731972565</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B431">
+        <v>0.0006980700060821429</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B432">
+        <v>0.00596532550652013</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B433">
+        <v>0.00596532550652013</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+        </is>
+      </c>
+      <c r="B434">
+        <v>0.02227477928498474</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B435">
+        <v>0.02227477928498474</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B436">
+        <v>1</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-ASSB.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-ASSB.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I436"/>
+  <dimension ref="A1:I550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="75" customWidth="1" min="1" max="1"/>
@@ -6434,7 +6434,9 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 One nominal installed kWh = 8.065117901632592 kg pack * 0.72591 kg cells/kg pack * 0.1708073285047623 kWh/kg cell. Published baseline cell design held constant at all scenario years. Manufacturing and end-of-life pack masses match. Cycle life/replacements belong to the consuming vehicle; no chemistry-specific lifetime is inferred.</t>
         </is>
@@ -6542,11 +6544,11 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB polymer, separated-controls engineering reference</t>
+          <t>market for battery cells, ASSB, polymer, density-scaled reference</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>7.696378455192915</v>
+        <v>5.854549735974115</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -6565,7 +6567,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB polymer, separated-controls engineering reference</t>
+          <t>market for battery cells, ASSB, polymer, density-scaled reference</t>
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
@@ -6573,11 +6575,11 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>market for used Li-ion battery</t>
+          <t>battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>-7.696378455192915</v>
+        <v>1</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -6586,7 +6588,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -6596,7 +6598,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>used Li-ion battery</t>
+          <t>battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -7647,7 +7649,9 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 One nominal installed kWh = 4.357203948791617 kg pack * 0.72591 kg cells/kg pack * 0.3161617539697314 kWh/kg cell. Published baseline cell design held constant at all scenario years. Manufacturing and end-of-life pack masses match. Cycle life/replacements belong to the consuming vehicle; no chemistry-specific lifetime is inferred.</t>
         </is>
@@ -7755,11 +7759,11 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB oxidic, separated-controls engineering reference</t>
+          <t>market for battery cells, ASSB, oxidic, density-scaled reference</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>4.157991365454557</v>
+        <v>3.162937918467323</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -7778,7 +7782,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB oxidic, separated-controls engineering reference</t>
+          <t>market for battery cells, ASSB, oxidic, density-scaled reference</t>
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
@@ -7786,11 +7790,11 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>market for used Li-ion battery</t>
+          <t>battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>-4.157991365454557</v>
+        <v>1</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -7799,7 +7803,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -7809,7 +7813,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>used Li-ion battery</t>
+          <t>battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -8860,7 +8864,9 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 One nominal installed kWh = 4.350854113378415 kg pack * 0.72591 kg cells/kg pack * 0.3166231748883239 kWh/kg cell. Published baseline cell design held constant at all scenario years. Manufacturing and end-of-life pack masses match. Cycle life/replacements belong to the consuming vehicle; no chemistry-specific lifetime is inferred.</t>
         </is>
@@ -8968,11 +8974,11 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB sulfidic, separated-controls engineering reference</t>
+          <t>market for battery cells, ASSB, sulfidic, density-scaled reference</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>4.151931846292625</v>
+        <v>3.1583285094425255</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -8991,7 +8997,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB sulfidic, separated-controls engineering reference</t>
+          <t>market for battery cells, ASSB, sulfidic, density-scaled reference</t>
         </is>
       </c>
       <c r="H363" t="inlineStr"/>
@@ -8999,11 +9005,11 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>market for used Li-ion battery</t>
+          <t>battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>-4.151931846292625</v>
+        <v>1</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -9012,7 +9018,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -9022,7 +9028,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>used Li-ion battery</t>
+          <t>battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -10831,6 +10837,2502 @@
       <c r="I436" t="inlineStr">
         <is>
           <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, polymer, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B441">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, polymer, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, polymer, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="B448">
+        <v>1</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, polymer, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, polymer, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>battery cell production, ASSB, polymer</t>
+        </is>
+      </c>
+      <c r="B449">
+        <v>1</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>battery cell, ASSB, polymer</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>battery cell, ASSB, polymer</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B450">
+        <v>-1</v>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B455">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="B462">
+        <v>1</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B463">
+        <v>0.02539779724194578</v>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B464">
+        <v>0.02539779724194578</v>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B465">
+        <v>1.380761015441937</v>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B466">
+        <v>1.380761015441937</v>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B467">
+        <v>0.04151563010702675</v>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B468">
+        <v>0.005372610955026991</v>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B469">
+        <v>0.04591140270659429</v>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B470">
+        <v>0.04591140270659429</v>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+        </is>
+      </c>
+      <c r="B471">
+        <v>0.171435131383134</v>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B472">
+        <v>0.171435131383134</v>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B473">
+        <v>7.696378455192915</v>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B474">
+        <v>-1.8418287192187994</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, oxidic, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B479">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, oxidic, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, oxidic, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="B486">
+        <v>1</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, oxidic, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, oxidic, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>battery cell production, ASSB, oxidic</t>
+        </is>
+      </c>
+      <c r="B487">
+        <v>1</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>battery cell, ASSB, oxidic</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>battery cell, ASSB, oxidic</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B488">
+        <v>-1</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B493">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="B500">
+        <v>1</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B501">
+        <v>0.013721235545832976</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B502">
+        <v>0.013721235545832976</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B503">
+        <v>0.7459602478474967</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B504">
+        <v>0.7459602478474967</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B505">
+        <v>0.02242894271915006</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B506">
+        <v>0.0029025690577723605</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B507">
+        <v>0.024803771948236533</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B508">
+        <v>0.024803771948236533</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+        </is>
+      </c>
+      <c r="B509">
+        <v>0.09261833993437259</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B510">
+        <v>0.09261833993437259</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B511">
+        <v>4.157991365454557</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B512">
+        <v>-0.9950534469872342</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, sulfidic, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B517">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, sulfidic, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, sulfidic, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="B524">
+        <v>1</v>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, sulfidic, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>market for battery cells, ASSB, sulfidic, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>battery cell production, ASSB, sulfidic</t>
+        </is>
+      </c>
+      <c r="B525">
+        <v>1</v>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>battery cell, ASSB, sulfidic</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>battery cell, ASSB, sulfidic</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B526">
+        <v>-1</v>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B531">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="B538">
+        <v>1</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B539">
+        <v>0.013701239330735911</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B540">
+        <v>0.013701239330735911</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B541">
+        <v>0.7448731459228928</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B542">
+        <v>0.7448731459228928</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B543">
+        <v>0.02239625659831832</v>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B544">
+        <v>0.0028983390891941354</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B545">
+        <v>0.024767624944022612</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B546">
+        <v>0.024767624944022612</v>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>ethylene glycols production, thermal hydrolysis of ethylene oxide</t>
+        </is>
+      </c>
+      <c r="B547">
+        <v>0.0924833654824674</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B548">
+        <v>0.0924833654824674</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B549">
+        <v>4.151931846292625</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B550">
+        <v>-0.993603336850099</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-ASSB.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-ASSB.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>polyethylene oxide production, proxy, for ASSB</t>
+          <t xml:space="preserve">polyethylene oxide production, for ASSB</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,8 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Material proxy: one kg ethylene oxide per kg addition polymer. Corrects the polyethylene label in Zhang 2025 S12 to the named PEO chemistry. Polymerization energy and catalyst inventory remain a coverage gap; electrolyte mixing/heating/drying is supplied separately. https://doi.org/10.1016/j.jclepro.2025.146607</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: polyethylene oxide production, proxy, for ASSB. Former reference product: polyethylene oxide, for ASSB. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+Material proxy: one kg ethylene oxide per kg addition polymer. Corrects the polyethylene label in Zhang 2025 S12 to the named PEO chemistry. Polymerization energy and catalyst inventory remain a coverage gap; electrolyte mixing/heating/drying is supplied separately. https://doi.org/10.1016/j.jclepro.2025.146607</t>
         </is>
       </c>
     </row>
@@ -568,7 +569,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>polyethylene oxide production, proxy, for ASSB</t>
+          <t xml:space="preserve">polyethylene oxide production, for ASSB</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -790,7 +791,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>polyethylene oxide production, proxy, for ASSB</t>
+          <t xml:space="preserve">polyethylene oxide production, for ASSB</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6544,7 +6545,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, polymer, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, ASSB, polymer, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -6567,7 +6568,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, polymer, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, ASSB, polymer, including end-of-life treatment</t>
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
@@ -6575,7 +6576,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, ASSB, polymer, without cells and controls</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -6598,7 +6599,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, ASSB, polymer, without cells and controls</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -6610,7 +6611,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC955</t>
         </is>
       </c>
       <c r="B249">
@@ -6633,7 +6634,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC955</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7760,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, oxidic, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, ASSB, oxidic, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -7782,7 +7783,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, oxidic, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, ASSB, oxidic, including end-of-life treatment</t>
         </is>
       </c>
       <c r="H305" t="inlineStr"/>
@@ -7790,7 +7791,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, ASSB, oxidic, without cells and controls</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -7813,7 +7814,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, ASSB, oxidic, without cells and controls</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -7825,7 +7826,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC955</t>
         </is>
       </c>
       <c r="B307">
@@ -7848,7 +7849,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC955</t>
         </is>
       </c>
     </row>
@@ -8974,7 +8975,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, sulfidic, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, ASSB, sulfidic, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -8997,7 +8998,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, sulfidic, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, ASSB, sulfidic, including end-of-life treatment</t>
         </is>
       </c>
       <c r="H363" t="inlineStr"/>
@@ -9005,7 +9006,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, ASSB, sulfidic, without cells and controls</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -9028,7 +9029,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, ASSB, sulfidic, without cells and controls</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -9040,7 +9041,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC955</t>
         </is>
       </c>
       <c r="B365">
@@ -9063,7 +9064,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC955</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9076,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB polymer, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack production, ASSB, polymer, without central controls</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9110,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB polymer, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack, ASSB, polymer, without central controls</t>
         </is>
       </c>
     </row>
@@ -9145,7 +9146,8 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery hardware, ASSB polymer, separated-controls engineering reference. Former reference product: battery hardware, ASSB polymer, separated-controls engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9208,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB polymer, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack production, ASSB, polymer, without central controls</t>
         </is>
       </c>
       <c r="B376">
@@ -9229,12 +9231,12 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB polymer, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack, ASSB, polymer, without central controls</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB polymer, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack, ASSB, polymer, without central controls</t>
         </is>
       </c>
     </row>
@@ -9666,7 +9668,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB oxidic, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack production, ASSB, oxidic, without central controls</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9702,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB oxidic, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack, ASSB, oxidic, without central controls</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9738,8 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery hardware, ASSB oxidic, separated-controls engineering reference. Former reference product: battery hardware, ASSB oxidic, separated-controls engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.</t>
         </is>
       </c>
     </row>
@@ -9797,7 +9800,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB oxidic, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack production, ASSB, oxidic, without central controls</t>
         </is>
       </c>
       <c r="B400">
@@ -9820,12 +9823,12 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB oxidic, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack, ASSB, oxidic, without central controls</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB oxidic, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack, ASSB, oxidic, without central controls</t>
         </is>
       </c>
     </row>
@@ -10257,7 +10260,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB sulfidic, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack production, ASSB, sulfidic, without central controls</t>
         </is>
       </c>
     </row>
@@ -10291,7 +10294,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB sulfidic, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack, ASSB, sulfidic, without central controls</t>
         </is>
       </c>
     </row>
@@ -10327,7 +10330,8 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery hardware, ASSB sulfidic, separated-controls engineering reference. Former reference product: battery hardware, ASSB sulfidic, separated-controls engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ASSB CONTROL/STRUCTURE BOUNDARY, issue54, 2026-10-18. Approved ASSB reference cell designs in this workbook; Crenna2021 DOI10.1016/j.resconrec.2021.105619 public pack framework; existing independently separated16-module/central-control reference from issues14/35.143kg and16modules are declared pack-architecture assumptions, not published complete ASSB packs. Retain each approved polymer/oxide/sulfide cell recipe and its baseline manufactured cell quantity per gross nominalkWh. Replace the active whole-BMS+module-packaging+unspecified-passive aggregate by one explicit control package per143kg reference completepack:16modulemonitorboards,onecentralcontroller/protection and its retained regulator allowance, already supplied by battery monitoring and central controls,NMC955 reference. This is an engineering architecture transfer, not a measured ASSB topology; channel/voltage/cellformat and packmass need design verification. Existing controls6.538kg/reference143kg; retain cellshare0.72591 of complete baselinepack. Remaining non-electronic mass uses existing public Crenna/Dai bulk pack proportions with50/50glycol/water, not a second module-board purchase. New perkg hardware excludes controls; divide cell and passive quantities by1-6.538/143 to maintain one kg of this hardware. At capacity level buy originalcompletepackkg*(1-6.538/143), plus originalcompletepackkg/143 units of controls. Net completepack mass and cellcapacity unchanged at baseline. Existing density learning now scales kg hardware only, while explicit control count per nominalkWh stays fixed. Control helper already disposes its6.538kg: local usedbattery treatment equals only noncontrol hardware mass, preserving complete disposal once. Source processservices retained as engineering assembly proxies scaled to hardware mass; no new measured yields, invented minor-metal filler, annualprocurement or primary-secondaryclaims. Additional assembly energy1kWh/kg is an explicit reference; packagingtransport/thermalqualification are gaps. Legacy wholepack producers remain available for other users but active capacity references no longer call them. This is a correction of explicit allocation boundaries, not proof of realfuture ASSB lifetime or practical energy density. Test reference architecture100-200kg and8-24modules, holding completepack/cellmass coherent.</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10392,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB sulfidic, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack production, ASSB, sulfidic, without central controls</t>
         </is>
       </c>
       <c r="B424">
@@ -10411,12 +10415,12 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB sulfidic, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack, ASSB, sulfidic, without central controls</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>battery hardware, ASSB sulfidic, separated-controls engineering reference</t>
+          <t xml:space="preserve">battery pack, ASSB, sulfidic, without central controls</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10852,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, polymer, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, ASSB, polymer, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10886,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, polymer, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, ASSB, polymer, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10922,8 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cells, ASSB, polymer, density-scaled reference. Former reference product: market for battery cells, ASSB, polymer, density-scaled reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10984,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, polymer, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, ASSB, polymer, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B448">
@@ -11002,12 +11007,12 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, polymer, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, ASSB, polymer, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, polymer, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, ASSB, polymer, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11094,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, ASSB, polymer, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11128,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, ASSB, polymer, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11164,9 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference. Former reference product: battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11227,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, ASSB, polymer, without cells and controls</t>
         </is>
       </c>
       <c r="B462">
@@ -11243,12 +11250,12 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, ASSB, polymer, without cells and controls</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, ASSB, polymer, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -11680,7 +11687,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, oxidic, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, ASSB, oxidic, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -11714,7 +11721,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, oxidic, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, ASSB, oxidic, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11757,8 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cells, ASSB, oxidic, density-scaled reference. Former reference product: market for battery cells, ASSB, oxidic, density-scaled reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11819,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, oxidic, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, ASSB, oxidic, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B486">
@@ -11834,12 +11842,12 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, oxidic, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, ASSB, oxidic, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, oxidic, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, ASSB, oxidic, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -11921,7 +11929,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, ASSB, oxidic, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -11955,7 +11963,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, ASSB, oxidic, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -11991,7 +11999,9 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference. Former reference product: battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12062,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, ASSB, oxidic, without cells and controls</t>
         </is>
       </c>
       <c r="B500">
@@ -12075,12 +12085,12 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, ASSB, oxidic, without cells and controls</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, ASSB, oxidic, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -12512,7 +12522,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, sulfidic, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, ASSB, sulfidic, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -12546,7 +12556,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, sulfidic, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, ASSB, sulfidic, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -12582,7 +12592,8 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cells, ASSB, sulfidic, density-scaled reference. Former reference product: market for battery cells, ASSB, sulfidic, density-scaled reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -12643,7 +12654,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, sulfidic, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, ASSB, sulfidic, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B524">
@@ -12666,12 +12677,12 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, sulfidic, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, ASSB, sulfidic, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>market for battery cells, ASSB, sulfidic, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, ASSB, sulfidic, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -12753,7 +12764,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, ASSB, sulfidic, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -12787,7 +12798,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, ASSB, sulfidic, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -12823,7 +12834,9 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference. Former reference product: battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12897,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, ASSB, sulfidic, without cells and controls</t>
         </is>
       </c>
       <c r="B538">
@@ -12907,12 +12920,12 @@
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, ASSB, sulfidic, without cells and controls</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, ASSB, sulfidic, without cells and controls</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-ASSB.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-ASSB.xlsx
@@ -6589,7 +6589,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -6599,12 +6599,13 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, ASSB, polymer, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, ASSB, polymer, without cells and controls</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Equal-mass generic Li-ion end-of-life treatment proxy; no ASSB-specific recovery yield claimed.</t>
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Equal-mass generic Li-ion end-of-life treatment proxy; no ASSB-specific recovery yield claimed.</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7805,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -7814,12 +7815,13 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, ASSB, oxidic, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, ASSB, oxidic, without cells and controls</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Equal-mass generic Li-ion end-of-life treatment proxy; no ASSB-specific recovery yield claimed.</t>
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Equal-mass generic Li-ion end-of-life treatment proxy; no ASSB-specific recovery yield claimed.</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9021,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -9029,12 +9031,13 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, ASSB, sulfidic, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, ASSB, sulfidic, without cells and controls</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Equal-mass generic Li-ion end-of-life treatment proxy; no ASSB-specific recovery yield claimed.</t>
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Equal-mass generic Li-ion end-of-life treatment proxy; no ASSB-specific recovery yield claimed.</t>
         </is>
       </c>
     </row>
@@ -11128,7 +11131,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, ASSB, polymer, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, ASSB, polymer, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -11140,7 +11143,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
@@ -11164,7 +11167,8 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference. Former reference product: battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference. Former reference product: battery fixed noncell hardware, ASSB, polymer, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
 APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
@@ -11240,7 +11244,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -11250,12 +11254,12 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, ASSB, polymer, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, ASSB, polymer, without cells and controls</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, ASSB, polymer, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, ASSB, polymer, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -11963,7 +11967,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, ASSB, oxidic, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, ASSB, oxidic, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -11975,7 +11979,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
@@ -11999,7 +12003,8 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference. Former reference product: battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference. Former reference product: battery fixed noncell hardware, ASSB, oxidic, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
 APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
@@ -12075,7 +12080,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
@@ -12085,12 +12090,12 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, ASSB, oxidic, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, ASSB, oxidic, without cells and controls</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, ASSB, oxidic, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, ASSB, oxidic, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12803,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, ASSB, sulfidic, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, ASSB, sulfidic, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12815,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12839,8 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference. Former reference product: battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference. Former reference product: battery fixed noncell hardware, ASSB, sulfidic, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
 APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
@@ -12910,7 +12916,7 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
@@ -12920,12 +12926,12 @@
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, ASSB, sulfidic, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, ASSB, sulfidic, without cells and controls</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, ASSB, sulfidic, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, ASSB, sulfidic, without cells and controls</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-ASSB.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-ASSB.xlsx
@@ -6461,7 +6461,7 @@
       </ns0:c>
       <ns0:c r="B243" t="inlineStr">
         <ns0:is>
-          <ns0:t>market for battery capacity, ASSB, polymer</ns0:t>
+          <ns0:t xml:space="preserve">market for battery capacity, all-solid-state battery, polymer</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -6623,7 +6623,7 @@
     <ns0:row r="255">
       <ns0:c r="A255" t="inlineStr">
         <ns0:is>
-          <ns0:t>market for battery capacity, ASSB, polymer</ns0:t>
+          <ns0:t xml:space="preserve">market for battery capacity, all-solid-state battery, polymer</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B255" t="n">
@@ -7713,7 +7713,7 @@
       </ns0:c>
       <ns0:c r="B304" t="inlineStr">
         <ns0:is>
-          <ns0:t>market for battery capacity, ASSB, oxidic</ns0:t>
+          <ns0:t xml:space="preserve">market for battery capacity, all-solid-state battery, oxidic</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -7875,7 +7875,7 @@
     <ns0:row r="316">
       <ns0:c r="A316" t="inlineStr">
         <ns0:is>
-          <ns0:t>market for battery capacity, ASSB, oxidic</ns0:t>
+          <ns0:t xml:space="preserve">market for battery capacity, all-solid-state battery, oxidic</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B316" t="n">
@@ -8965,7 +8965,7 @@
       </ns0:c>
       <ns0:c r="B365" t="inlineStr">
         <ns0:is>
-          <ns0:t>market for battery capacity, ASSB, sulfidic</ns0:t>
+          <ns0:t xml:space="preserve">market for battery capacity, all-solid-state battery, sulfidic</ns0:t>
         </ns0:is>
       </ns0:c>
     </ns0:row>
@@ -9127,7 +9127,7 @@
     <ns0:row r="377">
       <ns0:c r="A377" t="inlineStr">
         <ns0:is>
-          <ns0:t>market for battery capacity, ASSB, sulfidic</ns0:t>
+          <ns0:t xml:space="preserve">market for battery capacity, all-solid-state battery, sulfidic</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="B377" t="n">
